--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754228</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135754209</v>
       </c>
       <c r="B7" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135754226</v>
       </c>
       <c r="B8" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135754210</v>
       </c>
       <c r="B9" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135754221</v>
       </c>
       <c r="B10" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754228</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754228</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754228</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 32102-2026 artfynd.xlsx
+++ b/artfynd/A 32102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754225</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754217</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754219</v>
       </c>
       <c r="B4" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754227</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754228</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135754212</v>
       </c>
       <c r="B11" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135754213</v>
       </c>
       <c r="B12" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135754214</v>
       </c>
       <c r="B13" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135754215</v>
       </c>
       <c r="B14" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135754216</v>
       </c>
       <c r="B15" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>135754222</v>
       </c>
       <c r="B16" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135754223</v>
       </c>
       <c r="B17" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>135754224</v>
       </c>
       <c r="B18" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>135754229</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135754230</v>
       </c>
       <c r="B20" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>135754231</v>
       </c>
       <c r="B21" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135754218</v>
       </c>
       <c r="B22" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
